--- a/zapros-assortiment.xlsx
+++ b/zapros-assortiment.xlsx
@@ -985,7 +985,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Просим подтвердить, что эти нетто ещё действуют, и написать, какая скидка возможна по дилерской схеме. Количество — наш черновик первого заказа, не заявка. FLY в инвойсе есть, в первый заказ не берём.</t>
+          <t>Просим подтвердить, что эти нетто ещё действуют, и написать, какая скидка возможна по дилерской схеме. Количество — черновик первого заказа на один куб, не заявка. BLASTER и FLY в инвойсе есть, в этот куб не берём.</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
         <v>46</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E5" s="8">
         <f>C5*D5</f>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>Самая сильная экономика среди редукторов</t>
+          <t>В первый куб, около 20 шт</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E6" s="8">
         <f>C6*D6</f>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>До ~250 л.с.</t>
+          <t>В первый куб, около 20 шт</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E7" s="8">
         <f>C7*D7</f>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Самый частый редуктор, до ~170 л.с.</t>
+          <t>В первый куб, около 20 шт</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>4.5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="E8" s="8">
         <f>C8*D8</f>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Основной фильтр в заказе</t>
+          <t>Основной фильтр в кубе, около 400 шт</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
         <v>3.5</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="E9" s="8">
         <f>C9*D9</f>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Второй фильтр, штук меньше</t>
+          <t>В инвойсе есть. В этот куб не берём</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
         <v>0.7</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>1200</v>
+        <v>250</v>
       </c>
       <c r="E10" s="8">
         <f>C10*D10</f>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Ходовой расходник</t>
+          <t>Ходовой расходник, около 250 шт</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>В инвойсе есть. В первый заказ не берём</t>
+          <t>В инвойсе есть. В этот куб не берём</t>
         </is>
       </c>
     </row>

--- a/zapros-assortiment.xlsx
+++ b/zapros-assortiment.xlsx
@@ -985,7 +985,7 @@
     <row r="2" ht="48" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Просим подтвердить, что эти нетто ещё действуют, и написать, какая скидка возможна по дилерской схеме. Количество — черновик первого заказа на один куб, не заявка. BLASTER и FLY в инвойсе есть, в этот куб не берём.</t>
+          <t>Первый заказ смотрим как 130 шт AT13 XP. Остальное из инвойса в этот заход не берём. Просим подтвердить 46 € и написать скидку по дилерской схеме. Количество — черновик, не заявка.</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
         <v>46</v>
       </c>
       <c r="D5" s="7" t="n">
-        <v>20</v>
+        <v>130</v>
       </c>
       <c r="E5" s="8">
         <f>C5*D5</f>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>В первый куб, около 20 шт</t>
+          <t>Первый заказ, около 130 шт</t>
         </is>
       </c>
     </row>
@@ -1063,7 +1063,7 @@
         <v>34</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E6" s="8">
         <f>C6*D6</f>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>В первый куб, около 20 шт</t>
+          <t>В инвойсе есть. В этот заказ не берём</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         <v>26</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E7" s="8">
         <f>C7*D7</f>
@@ -1098,7 +1098,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>В первый куб, около 20 шт</t>
+          <t>В инвойсе есть. В этот заказ не берём</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>4.5</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E8" s="8">
         <f>C8*D8</f>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Основной фильтр в кубе, около 400 шт</t>
+          <t>В инвойсе есть. В этот заказ не берём</t>
         </is>
       </c>
     </row>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>В инвойсе есть. В этот куб не берём</t>
+          <t>В инвойсе есть. В этот заказ не берём</t>
         </is>
       </c>
     </row>
@@ -1171,7 +1171,7 @@
         <v>0.7</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="E10" s="8">
         <f>C10*D10</f>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Ходовой расходник, около 250 шт</t>
+          <t>В инвойсе есть. В этот заказ не берём</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>В инвойсе есть. В этот куб не берём</t>
+          <t>В инвойсе есть. В этот заказ не берём</t>
         </is>
       </c>
     </row>

--- a/zapros-assortiment.xlsx
+++ b/zapros-assortiment.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet name="Нет вашей цены" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Уже есть в инвойсе" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Два черновика заказа" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Нет вашей цены'!$A$4:$F$17</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Нет вашей цены'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Уже есть в инвойсе'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Два черновика заказа'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="# ##0"/>
     <numFmt numFmtId="165" formatCode="# ##0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,11 +53,6 @@
     </font>
     <font>
       <name val="Calibri"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -100,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -115,18 +110,9 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -510,10 +496,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="48" customHeight="1">
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Это не анкета и заполнять её не нужно. Удобнее прислать ваш полный прайс или типовой инвойс: нетто в евро, наличие, срок. Мы сами сопоставим. Полкой Digitronic ниже указана розница в России, это не ваша цена.</t>
+          <t>Это не анкета, заполнять её не нужно. Удобнее прислать полный прайс: нетто в евро, наличие, срок. Полка Digitronic — розница в России, не ваша цена.</t>
         </is>
       </c>
     </row>
@@ -635,7 +621,7 @@
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Дороже обычного MP48, в наличии</t>
+          <t>Дороже обычного MP48</t>
         </is>
       </c>
     </row>
@@ -947,14 +933,6 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;LГБО · позиции без вашей цены</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
 
@@ -964,58 +942,64 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="52" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Позиции, цена которых у нас уже есть</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="48" customHeight="1">
+          <t>Два черновика первого заказа. Это альтернативы, количества не складывать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Первый заказ смотрим как 130 шт AT13 XP. Остальное из инвойса в этот заход не берём. Просим подтвердить 46 € и написать скидку по дилерской схеме. Количество — черновик, не заявка.</t>
+          <t>Просим подтвердить нетто из инвойса и написать возможную дилерскую скидку. Количество — ориентир, не заявка.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Вариант</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>Название</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Артикул</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Цена в инвойсе, €</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Смотрим в первый заказ, шт</t>
-        </is>
-      </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Сумма по инвойсу, €</t>
+          <t>Штук</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Сумма, €</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>Комментарий</t>
         </is>
@@ -1024,216 +1008,268 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>Один артикул</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
           <t>AT13 XP</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>RGDG3990</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="D5" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="E5" s="5" t="n">
         <v>130</v>
       </c>
-      <c r="E5" s="8">
-        <f>C5*D5</f>
+      <c r="F5" s="6">
+        <f>D5*E5</f>
         <v/>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Первый заказ, около 130 шт</t>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Основной вариант</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>AT09 Nordic XP</t>
+          <t>Комплект на куб</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>RGDG3895</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>34</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="8">
-        <f>C6*D6</f>
+          <t>BLASTER Y 12×2/12</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>BLASTER Y 12x2/12</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="F6" s="6">
+        <f>D6*E6</f>
         <v/>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>В инвойсе есть. В этот заказ не берём</t>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Фильтр</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>AT09 Nordic</t>
+          <t>Комплект на куб</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>RGDG3890</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="D7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="8">
-        <f>C7*D7</f>
+          <t>FLS 12×12</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>FL01S 12/12</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="F7" s="6">
+        <f>D7*E7</f>
         <v/>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>В инвойсе есть. В этот заказ не берём</t>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Фильтр</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>BLASTER Y 12×2/12</t>
+          <t>Комплект на куб</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BLASTER Y 12x2/12</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="8">
-        <f>C8*D8</f>
+          <t>AT09 Nordic</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>RGDG3890</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" s="6">
+        <f>D8*E8</f>
         <v/>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>В инвойсе есть. В этот заказ не берём</t>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Редуктор</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>BLASTER 12×12</t>
+          <t>Комплект на куб</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BLASTER 12х12</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="8">
-        <f>C9*D9</f>
+          <t>AT09 Nordic XP</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>RGDG3895</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="F9" s="6">
+        <f>D9*E9</f>
         <v/>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>В инвойсе есть. В этот заказ не берём</t>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Редуктор</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>FLS 12×12</t>
+          <t>Комплект на куб</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>FL01S 12/12</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="8">
-        <f>C10*D10</f>
+          <t>AT13 XP</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>RGDG3990</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" s="6">
+        <f>D10*E10</f>
         <v/>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>В инвойсе есть. В этот заказ не берём</t>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Редуктор</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>Не берём</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>BLASTER 12×12</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>BLASTER 12х12</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>В инвойсе есть, в эти черновики не входит</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Не берём</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
           <t>FLY 12 / 2×12</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>FL01Y 12/12</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="D12" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="E12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="8">
-        <f>C11*D11</f>
+      <c r="F12" s="6">
+        <f>D12*E12</f>
         <v/>
       </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>В инвойсе есть. В этот заказ не берём</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Итого в черновике</t>
-        </is>
-      </c>
-      <c r="D12" s="10">
-        <f>SUM(D5:D11)</f>
-        <v/>
-      </c>
-      <c r="E12" s="11">
-        <f>SUM(E5:E11)</f>
-        <v/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>В инвойсе есть, в эти черновики не входит</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;LГБО · черновик первого заказа</oddHeader>
+    <oddHeader>&amp;LГБО · черновики первого заказа</oddHeader>
     <oddFooter/>
     <evenHeader/>
     <evenFooter/>

--- a/zapros-assortiment.xlsx
+++ b/zapros-assortiment.xlsx
@@ -7,13 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Нет вашей цены" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Два черновика заказа" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Нет в инвойсе" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Составы в евро" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Нет вашей цены'!$A$4:$F$17</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Нет вашей цены'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Два черновика заказа'!$1:$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Нет в инвойсе'!$A$4:$D$17</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Нет в инвойсе'!$1:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Составы в евро'!$1:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -95,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -107,8 +107,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -478,28 +481,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Позиции, по которым у нас нет вашей цены</t>
+          <t>Артикулы, которых не было в прошлом инвойсе</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Это не анкета, заполнять её не нужно. Удобнее прислать полный прайс: нетто в евро, наличие, срок. Полка Digitronic — розница в России, не ваша цена.</t>
+          <t>Это не анкета. Удобнее прислать полный прайс: нетто в евро или в злотых, наличие и срок. Мы сами сопоставим.</t>
         </is>
       </c>
     </row>
@@ -521,17 +522,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Полка Digitronic, ₽</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Наличие у Digitronic</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Зачем смотрим</t>
+          <t>Что хотим увидеть в прайсе</t>
         </is>
       </c>
     </row>
@@ -551,17 +542,9 @@
           <t>616000573</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>13200</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>много</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Ходовой комплект 4 цил.</t>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -581,17 +564,9 @@
           <t>616000087</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>15600</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>много</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Ходовой комплект 4 цил.</t>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -611,17 +586,9 @@
           <t>616000089</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>18200</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>много</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Дороже обычного MP48</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -641,17 +608,9 @@
           <t>WEG-AMD024409999-000</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
-        <v>13300</v>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>На российской полке нет в наличии</t>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -671,17 +630,9 @@
           <t>WEG-AMD028409999-300</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
-        <v>23500</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>На российской полке нет в наличии</t>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -701,17 +652,9 @@
           <t>WEG-AMD030609999-300</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>23300</v>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>На российской полке нет в наличии</t>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -731,17 +674,9 @@
           <t>WEG-AMD030809999-300</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
-        <v>28000</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>нет</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>На российской полке нет в наличии</t>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -761,17 +696,9 @@
           <t>MVDG0205.1</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>5550</v>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>много</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>Класс A</t>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -791,17 +718,9 @@
           <t>MVDG0012</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
-        <v>4150</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>много</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>С заправочным устройством</t>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -821,17 +740,9 @@
           <t>620500170</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
-        <v>8000</v>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>много</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Форсуночная рейка</t>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -851,17 +762,9 @@
           <t>33.EVG.13</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
-        <v>5550</v>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>много</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Форсуночная рейка</t>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -881,17 +784,9 @@
           <t>TP6-48</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n">
-        <v>11300</v>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>много</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Термопластик</t>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
@@ -911,25 +806,17 @@
           <t>ТР8-48</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>13900</v>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>много</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Термопластик</t>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>нетто, наличие, срок</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F17"/>
+  <autoFilter ref="A4:D17"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
@@ -942,36 +829,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Два черновика первого заказа. Это альтернативы, количества не складывать.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
+          <t>Два состава по прошлому инвойсу. Это альтернативы, количества не складывать.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Просим подтвердить нетто из инвойса и написать возможную дилерскую скидку. Количество — ориентир, не заявка.</t>
+          <t>Просим подтвердить нетто в евро и написать, какая индивидуальная цена возможна. Если у вас прайс в злотых, можно прислать в злотых. Количество — ориентир, не заявка.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Вариант</t>
+          <t>Состав</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -997,18 +883,13 @@
       <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Сумма, €</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>Комментарий</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Один артикул</t>
+          <t>Первый</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -1024,23 +905,18 @@
       <c r="D5" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>130</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="7">
         <f>D5*E5</f>
         <v/>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>Основной вариант</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Комплект на куб</t>
+          <t>Второй, комплект</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -1053,26 +929,21 @@
           <t>BLASTER Y 12x2/12</t>
         </is>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="5" t="n">
         <v>4.5</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>450</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="7">
         <f>D6*E6</f>
         <v/>
       </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>Фильтр</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Комплект на куб</t>
+          <t>Второй, комплект</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -1085,26 +956,21 @@
           <t>FL01S 12/12</t>
         </is>
       </c>
-      <c r="D7" s="6" t="n">
+      <c r="D7" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>200</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="7">
         <f>D7*E7</f>
         <v/>
       </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>Фильтр</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Комплект на куб</t>
+          <t>Второй, комплект</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -1120,23 +986,18 @@
       <c r="D8" s="5" t="n">
         <v>26</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="7">
         <f>D8*E8</f>
         <v/>
       </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>Редуктор</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Комплект на куб</t>
+          <t>Второй, комплект</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -1152,23 +1013,18 @@
       <c r="D9" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="7">
         <f>D9*E9</f>
         <v/>
       </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>Редуктор</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Комплект на куб</t>
+          <t>Второй, комплект</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -1184,97 +1040,20 @@
       <c r="D10" s="5" t="n">
         <v>46</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="7">
         <f>D10*E10</f>
         <v/>
       </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>Редуктор</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>Не берём</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>BLASTER 12×12</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>BLASTER 12х12</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6">
-        <f>D11*E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>В инвойсе есть, в эти черновики не входит</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>Не берём</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>FLY 12 / 2×12</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>FL01Y 12/12</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="6">
-        <f>D12*E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>В инвойсе есть, в эти черновики не входит</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader>&amp;LГБО · черновики первого заказа</oddHeader>
-    <oddFooter/>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
 </worksheet>
 </file>
--- a/zapros-assortiment.xlsx
+++ b/zapros-assortiment.xlsx
@@ -493,14 +493,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Артикулы, которых не было в прошлом инвойсе</t>
+          <t>Чего не было в инвойсе</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Это не анкета. Удобнее прислать полный прайс: нетто в евро или в злотых, наличие и срок. Мы сами сопоставим.</t>
+          <t>Заполнять не нужно. Проще прислать весь перечень: нетто в евро или в злотых, наличие и срок.</t>
         </is>
       </c>
     </row>
@@ -843,14 +843,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Два состава по прошлому инвойсу. Это альтернативы, количества не складывать.</t>
+          <t>Два варианта первого заказа. Это на выбор, не вместе.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Просим подтвердить нетто в евро и написать, какая индивидуальная цена возможна. Если у вас прайс в злотых, можно прислать в злотых. Количество — ориентир, не заявка.</t>
+          <t>Цены как в вашем инвойсе, в евро. Напишите, пожалуйста, какая индивидуальная цена возможна. Если прайс в злотых, можно в злотых.</t>
         </is>
       </c>
     </row>

--- a/zapros-assortiment.xlsx
+++ b/zapros-assortiment.xlsx
@@ -493,7 +493,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Чего не было в инвойсе</t>
+          <t>Позиции, по которым нужна цена</t>
         </is>
       </c>
     </row>
@@ -843,14 +843,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Два варианта первого заказа. Это на выбор, не вместе.</t>
+          <t>Два варианта заказа. На выбор, не вместе.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Цены как в вашем инвойсе, в евро. Напишите, пожалуйста, какая индивидуальная цена возможна. Если прайс в злотых, можно в злотых.</t>
+          <t>Цены в евро, как они у нас есть. Напишите, какая индивидуальная цена возможна. Если прайс в злотых, можно в злотых.</t>
         </is>
       </c>
     </row>

--- a/zapros-assortiment.xlsx
+++ b/zapros-assortiment.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="# ##0"/>
     <numFmt numFmtId="165" formatCode="# ##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,6 +54,9 @@
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -95,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -116,6 +119,7 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,13 +485,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,7 +505,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Заполнять не нужно. Проще прислать весь перечень: нетто в евро или в злотых, наличие и срок.</t>
+          <t>Кол-во — ориентир на первый пробный заказ (~5,5–6 тыс. € товар / до ~1 млн ₽ с доставкой и таможней). Точный состав по этим позициям — после ваших нетто. Можно прислать весь свой перечень.</t>
         </is>
       </c>
     </row>
@@ -525,6 +530,11 @@
           <t>Что хотим увидеть в прайсе</t>
         </is>
       </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Кол-во, шт (ориентир 1-й заказ)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -547,6 +557,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -569,6 +582,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>25</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -591,6 +607,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -613,6 +632,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -635,6 +657,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E9" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -657,6 +682,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -679,6 +707,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -701,6 +732,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E12" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -723,6 +757,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E13" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -745,6 +782,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -767,6 +807,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E15" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -789,6 +832,9 @@
           <t>нетто, наличие, срок</t>
         </is>
       </c>
+      <c r="E16" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -810,6 +856,9 @@
         <is>
           <t>нетто, наличие, срок</t>
         </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -843,14 +892,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Два варианта заказа. На выбор, не вместе.</t>
+          <t>Два варианта первого пробного заказа. На выбор, не вместе. Товар ~5,4–6,0 тыс. € (наш чек с логистикой/таможней до ~1 млн ₽).</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Цены в евро, как они у нас есть. Напишите, какая индивидуальная цена возможна. Если прайс в злотых, можно в злотых.</t>
+          <t>Кол-ва заполнены. Нужна ваша индивидуальная цена нетто EUR (или PLN) и условие скидки от суммы/количества.</t>
         </is>
       </c>
     </row>

--- a/zapros-assortiment.xlsx
+++ b/zapros-assortiment.xlsx
@@ -505,7 +505,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Кол-во — ориентир на первый пробный заказ (~5,5–6 тыс. € товар / до ~1 млн ₽ с доставкой и таможней). Точный состав по этим позициям — после ваших нетто. Можно прислать весь свой перечень.</t>
+          <t>Кол-во — ориентир на первый пробный заказ (~5–6 тыс. € по товару). Точный состав по этим позициям — после ваших нетто. Можно прислать весь свой перечень.</t>
         </is>
       </c>
     </row>
@@ -892,14 +892,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Два варианта первого пробного заказа. На выбор, не вместе. Товар ~5,4–6,0 тыс. € (наш чек с логистикой/таможней до ~1 млн ₽).</t>
+          <t>Два варианта первого пробного заказа. На выбор, не вместе. Ориентир ~5–6 тыс. € по товару.</t>
         </is>
       </c>
     </row>
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Кол-ва заполнены. Нужна ваша индивидуальная цена нетто EUR (или PLN) и условие скидки от суммы/количества.</t>
+          <t>Кол-ва заполнены. Нужна цена нетто EUR или PLN, наличие, срок и ваши условия на такой объём.</t>
         </is>
       </c>
     </row>
